--- a/data/demo/Штатное расписание 2026.xlsx
+++ b/data/demo/Штатное расписание 2026.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="сотрудники" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="120_надбавка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -430,6 +431,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +486,16 @@
           <t>дата окончания</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>разрешенные договоры</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>запрещенные договоры</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +544,11 @@
           <t>31.12.2026</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_GOZ-26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +597,11 @@
           <t>31.12.2026</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_GOZ-26, C_GRANT-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,7 +638,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>100000</v>
+        <v>160000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -625,6 +648,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_COM-26</t>
         </is>
       </c>
     </row>
@@ -663,7 +691,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>118000</v>
+        <v>130000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -673,6 +701,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_GOZ-26</t>
         </is>
       </c>
     </row>
@@ -723,6 +756,11 @@
           <t>31.12.2026</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>C_GRANT-26, C_PRI-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -750,7 +788,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>совместительство</t>
+          <t>основное</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -759,7 +797,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>55000</v>
+        <v>74824.45</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -769,6 +807,11 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_COM-26</t>
         </is>
       </c>
     </row>
@@ -807,7 +850,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -817,6 +860,16 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>C_BASE-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>C_GOZ-26</t>
         </is>
       </c>
     </row>
@@ -866,6 +919,183 @@
         <is>
           <t>31.12.2026</t>
         </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_GOZ-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Морозов Максим Михайлович</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ведущий программист</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Отдел 12</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>основное</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>основной</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>175000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>01.01.2026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>C_COM-26, C_PRI-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Никитин Никита Николаевич</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Инженер</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Отдел 12</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>основное</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>основной</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>108000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>01.01.2026</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>C_BASE-26, C_GOZ-26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>сотрудник</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>договор секретности</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ставка 120</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C_GOZ-26</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C_PRI-26</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
